--- a/prompt-coach/research/live-tests/fixtures/fr_flux_q3.xlsx
+++ b/prompt-coach/research/live-tests/fixtures/fr_flux_q3.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,6 +412,9 @@
       <c r="D1" t="str">
         <v>Change</v>
       </c>
+      <c r="E1" t="str">
+        <v>Note</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -483,9 +486,85 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG&amp;A detail</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Q2 FY26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Q3 FY26</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Change</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Note</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG&amp;A - Salaries</v>
+      </c>
+      <c r="B9">
+        <v>110</v>
+      </c>
+      <c r="C9">
+        <v>138</v>
+      </c>
+      <c r="D9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG&amp;A - Marketing</v>
+      </c>
+      <c r="B10">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>81</v>
+      </c>
+      <c r="D10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG&amp;A - Legal fees</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Includes 7 one-time settlement</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG&amp;A - Other</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>